--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128763925</v>
+        <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719139</v>
+        <v>719126</v>
       </c>
       <c r="R5" t="n">
-        <v>6374165</v>
+        <v>6374163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,51 +1046,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128758560</v>
+        <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1100,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719126</v>
+        <v>719139</v>
       </c>
       <c r="R6" t="n">
-        <v>6374163</v>
+        <v>6374165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,18 +1143,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1453,30 +1453,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128758571</v>
+        <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86999</v>
+        <v>86927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249249</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grynspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius olidoamethysteus s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1484,10 +1488,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>719140</v>
+        <v>719184</v>
       </c>
       <c r="R10" t="n">
-        <v>6373973</v>
+        <v>6373910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,46 +1539,42 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128763927</v>
+        <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>249249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grynspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius olidoamethysteus s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>719184</v>
+        <v>719140</v>
       </c>
       <c r="R11" t="n">
-        <v>6373910</v>
+        <v>6373973</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128763947</v>
+        <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86753</v>
+        <v>86903</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2429,16 +2429,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3712</v>
+        <v>1988</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>719124</v>
+        <v>719185</v>
       </c>
       <c r="R20" t="n">
-        <v>6374154</v>
+        <v>6373860</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,22 +2503,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128758595</v>
+        <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86903</v>
+        <v>86890</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>719185</v>
+        <v>719153</v>
       </c>
       <c r="R21" t="n">
-        <v>6373860</v>
+        <v>6373906</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128758613</v>
+        <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86890</v>
+        <v>86753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2623,21 +2623,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>719153</v>
+        <v>719124</v>
       </c>
       <c r="R22" t="n">
-        <v>6373906</v>
+        <v>6374154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,22 +2697,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128763913</v>
+        <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>90975</v>
+        <v>86890</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>719198</v>
+        <v>719165</v>
       </c>
       <c r="R23" t="n">
-        <v>6374009</v>
+        <v>6373921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2794,44 +2794,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128763935</v>
+        <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91001</v>
+        <v>90975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>719192</v>
+        <v>719198</v>
       </c>
       <c r="R24" t="n">
-        <v>6373934</v>
+        <v>6374009</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2903,32 +2903,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128758612</v>
+        <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>86890</v>
+        <v>91001</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>719165</v>
+        <v>719192</v>
       </c>
       <c r="R25" t="n">
-        <v>6373921</v>
+        <v>6373934</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2988,22 +2988,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128758615</v>
+        <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>86890</v>
+        <v>90888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,21 +3011,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>719126</v>
+        <v>719220</v>
       </c>
       <c r="R26" t="n">
-        <v>6374002</v>
+        <v>6374101</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3085,44 +3085,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128763940</v>
+        <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>90888</v>
+        <v>86775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4188</v>
+        <v>424</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>719220</v>
+        <v>719198</v>
       </c>
       <c r="R27" t="n">
-        <v>6374101</v>
+        <v>6373941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3194,32 +3194,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128763915</v>
+        <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>86775</v>
+        <v>98613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>424</v>
+        <v>219862</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>719198</v>
+        <v>719160</v>
       </c>
       <c r="R28" t="n">
-        <v>6373941</v>
+        <v>6374175</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128763932</v>
+        <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>98613</v>
+        <v>86890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219862</v>
+        <v>3674</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>719160</v>
+        <v>719126</v>
       </c>
       <c r="R29" t="n">
-        <v>6374175</v>
+        <v>6374002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3376,44 +3376,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128763924</v>
+        <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>86729</v>
+        <v>91001</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>719135</v>
+        <v>719216</v>
       </c>
       <c r="R30" t="n">
-        <v>6374160</v>
+        <v>6374124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3473,44 +3473,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128758594</v>
+        <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>91001</v>
+        <v>86729</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5747</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>719216</v>
+        <v>719135</v>
       </c>
       <c r="R31" t="n">
-        <v>6374124</v>
+        <v>6374160</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3570,12 +3570,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128763944</v>
+        <v>128758582</v>
       </c>
       <c r="B39" t="n">
-        <v>92790</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4273,37 +4273,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>719136</v>
+        <v>719122</v>
       </c>
       <c r="R39" t="n">
-        <v>6374164</v>
+        <v>6373999</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,51 +4341,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128763921</v>
+        <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>92768</v>
+        <v>86927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4398,10 +4394,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>719130</v>
+        <v>719119</v>
       </c>
       <c r="R40" t="n">
-        <v>6374157</v>
+        <v>6373869</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4442,28 +4438,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128763952</v>
+        <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>86890</v>
+        <v>92790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4471,34 +4468,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>719195</v>
+        <v>719136</v>
       </c>
       <c r="R41" t="n">
-        <v>6373936</v>
+        <v>6374164</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4539,6 +4539,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4557,10 +4558,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128758582</v>
+        <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>92768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4568,21 +4569,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4592,10 +4593,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>719122</v>
+        <v>719130</v>
       </c>
       <c r="R42" t="n">
-        <v>6373999</v>
+        <v>6374157</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4642,44 +4643,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128758574</v>
+        <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4689,10 +4690,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>719119</v>
+        <v>719195</v>
       </c>
       <c r="R43" t="n">
-        <v>6373869</v>
+        <v>6373936</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4733,19 +4734,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6125,45 +6125,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128758566</v>
+        <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>92791</v>
+        <v>86915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1438</v>
+        <v>462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Violettrandad spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Cortinarius pseudoglaucopus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>719264</v>
+        <v>719132</v>
       </c>
       <c r="R58" t="n">
-        <v>6373868</v>
+        <v>6374195</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6204,6 +6207,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6222,32 +6226,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128758583</v>
+        <v>128758566</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>92792</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>1438</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon leucopus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6261,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>719299</v>
+        <v>719264</v>
       </c>
       <c r="R59" t="n">
-        <v>6373884</v>
+        <v>6373868</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6319,32 +6323,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128758589</v>
+        <v>128758583</v>
       </c>
       <c r="B60" t="n">
-        <v>91001</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6354,10 +6358,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>719240</v>
+        <v>719299</v>
       </c>
       <c r="R60" t="n">
-        <v>6374049</v>
+        <v>6373884</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6416,32 +6420,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128758610</v>
+        <v>128758589</v>
       </c>
       <c r="B61" t="n">
-        <v>106911</v>
+        <v>91002</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221849</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6451,10 +6455,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>719323</v>
+        <v>719240</v>
       </c>
       <c r="R61" t="n">
-        <v>6374030</v>
+        <v>6374049</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6513,32 +6517,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128758587</v>
+        <v>128758610</v>
       </c>
       <c r="B62" t="n">
-        <v>91001</v>
+        <v>106916</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>221849</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>719350</v>
+        <v>719323</v>
       </c>
       <c r="R62" t="n">
-        <v>6373915</v>
+        <v>6374030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6610,10 +6614,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128758591</v>
+        <v>128758587</v>
       </c>
       <c r="B63" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6645,10 +6649,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>719264</v>
+        <v>719350</v>
       </c>
       <c r="R63" t="n">
-        <v>6374047</v>
+        <v>6373915</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,32 +6711,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128763941</v>
+        <v>128758591</v>
       </c>
       <c r="B64" t="n">
-        <v>90888</v>
+        <v>91002</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6742,10 +6746,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>719309</v>
+        <v>719264</v>
       </c>
       <c r="R64" t="n">
-        <v>6373758</v>
+        <v>6374047</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6792,44 +6796,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128758579</v>
+        <v>128763941</v>
       </c>
       <c r="B65" t="n">
-        <v>86927</v>
+        <v>90889</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>4188</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6843,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>719375</v>
+        <v>719309</v>
       </c>
       <c r="R65" t="n">
-        <v>6374079</v>
+        <v>6373758</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6883,51 +6887,50 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128763912</v>
+        <v>128758579</v>
       </c>
       <c r="B66" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6937,10 +6940,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>719273</v>
+        <v>719375</v>
       </c>
       <c r="R66" t="n">
-        <v>6374077</v>
+        <v>6374079</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6981,50 +6984,51 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128763920</v>
+        <v>128763912</v>
       </c>
       <c r="B67" t="n">
-        <v>92791</v>
+        <v>86972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1438</v>
+        <v>3767</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7034,10 +7038,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>719342</v>
+        <v>719273</v>
       </c>
       <c r="R67" t="n">
-        <v>6373936</v>
+        <v>6374077</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7096,32 +7100,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128758616</v>
+        <v>128763920</v>
       </c>
       <c r="B68" t="n">
-        <v>86890</v>
+        <v>92792</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>1438</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon leucopus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7131,10 +7135,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>719364</v>
+        <v>719342</v>
       </c>
       <c r="R68" t="n">
-        <v>6374088</v>
+        <v>6373936</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7181,44 +7185,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128758577</v>
+        <v>128758616</v>
       </c>
       <c r="B69" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7228,10 +7232,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>719343</v>
+        <v>719364</v>
       </c>
       <c r="R69" t="n">
-        <v>6374082</v>
+        <v>6374088</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7272,7 +7276,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7291,32 +7294,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128763902</v>
+        <v>128758577</v>
       </c>
       <c r="B70" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7326,10 +7329,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>719304</v>
+        <v>719343</v>
       </c>
       <c r="R70" t="n">
-        <v>6373952</v>
+        <v>6374082</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7370,50 +7373,51 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128763923</v>
+        <v>128763902</v>
       </c>
       <c r="B71" t="n">
-        <v>92768</v>
+        <v>86972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,10 +7427,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>719259</v>
+        <v>719304</v>
       </c>
       <c r="R71" t="n">
-        <v>6374086</v>
+        <v>6373952</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7485,32 +7489,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128763934</v>
+        <v>128763923</v>
       </c>
       <c r="B72" t="n">
-        <v>91001</v>
+        <v>92769</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7520,10 +7524,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>719273</v>
+        <v>719259</v>
       </c>
       <c r="R72" t="n">
-        <v>6374081</v>
+        <v>6374086</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7582,10 +7586,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128763905</v>
+        <v>128763934</v>
       </c>
       <c r="B73" t="n">
-        <v>86972</v>
+        <v>91002</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7593,21 +7597,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7617,10 +7621,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>719245</v>
+        <v>719273</v>
       </c>
       <c r="R73" t="n">
-        <v>6374105</v>
+        <v>6374081</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7679,32 +7683,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128758578</v>
+        <v>128763905</v>
       </c>
       <c r="B74" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7714,10 +7718,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>719382</v>
+        <v>719245</v>
       </c>
       <c r="R74" t="n">
-        <v>6374097</v>
+        <v>6374105</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7758,51 +7762,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128763938</v>
+        <v>128758578</v>
       </c>
       <c r="B75" t="n">
-        <v>56644</v>
+        <v>86927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>208260</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7812,10 +7815,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>719245</v>
+        <v>719382</v>
       </c>
       <c r="R75" t="n">
-        <v>6373863</v>
+        <v>6374097</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7856,21 +7859,119 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128763938</v>
+      </c>
+      <c r="B76" t="n">
+        <v>56644</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>719245</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6373863</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>86999</v>
+        <v>87026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>86999</v>
+        <v>87026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86903</v>
+        <v>86930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90889</v>
+        <v>90916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128758565</v>
       </c>
       <c r="B51" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86914</v>
+        <v>86941</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87121</v>
+        <v>87148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86915</v>
+        <v>86942</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128758566</v>
       </c>
       <c r="B59" t="n">
-        <v>92792</v>
+        <v>92819</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>128758589</v>
       </c>
       <c r="B61" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>128758610</v>
       </c>
       <c r="B62" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>128758587</v>
       </c>
       <c r="B63" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>128758591</v>
       </c>
       <c r="B64" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>128763941</v>
       </c>
       <c r="B65" t="n">
-        <v>90889</v>
+        <v>90916</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>128758579</v>
       </c>
       <c r="B66" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>128763912</v>
       </c>
       <c r="B67" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128763920</v>
       </c>
       <c r="B68" t="n">
-        <v>92792</v>
+        <v>92819</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>128758616</v>
       </c>
       <c r="B69" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>128758577</v>
       </c>
       <c r="B70" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128763902</v>
       </c>
       <c r="B71" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>128763923</v>
       </c>
       <c r="B72" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>128763934</v>
       </c>
       <c r="B73" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>128763905</v>
       </c>
       <c r="B74" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>128758578</v>
       </c>
       <c r="B75" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>128763938</v>
       </c>
       <c r="B76" t="n">
-        <v>56644</v>
+        <v>56671</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6226,48 +6226,51 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128758566</v>
+        <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>92819</v>
+        <v>87148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1438</v>
+        <v>451</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>719264</v>
+        <v>719183</v>
       </c>
       <c r="R59" t="n">
-        <v>6373868</v>
+        <v>6373851</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6299,56 +6302,62 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Bilder på Liams fynd. Finns ytterligare en inomhus på foten till höger PXL_20250928_195955265.RAW-01.COVER.jpg</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128758583</v>
+        <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>92819</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>1438</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon leucopus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6358,10 +6367,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>719299</v>
+        <v>719264</v>
       </c>
       <c r="R60" t="n">
-        <v>6373884</v>
+        <v>6373868</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6420,32 +6429,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128758589</v>
+        <v>128758583</v>
       </c>
       <c r="B61" t="n">
-        <v>91029</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6455,10 +6464,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>719240</v>
+        <v>719299</v>
       </c>
       <c r="R61" t="n">
-        <v>6374049</v>
+        <v>6373884</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6517,32 +6526,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128758610</v>
+        <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>106944</v>
+        <v>91029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221849</v>
+        <v>5747</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6552,10 +6561,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>719323</v>
+        <v>719240</v>
       </c>
       <c r="R62" t="n">
-        <v>6374030</v>
+        <v>6374049</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6614,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128758587</v>
+        <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>91029</v>
+        <v>106944</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5747</v>
+        <v>221849</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6649,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>719350</v>
+        <v>719323</v>
       </c>
       <c r="R63" t="n">
-        <v>6373915</v>
+        <v>6374030</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6711,7 +6720,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128758591</v>
+        <v>128758587</v>
       </c>
       <c r="B64" t="n">
         <v>91029</v>
@@ -6746,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>719264</v>
+        <v>719350</v>
       </c>
       <c r="R64" t="n">
-        <v>6374047</v>
+        <v>6373915</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6808,32 +6817,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128763941</v>
+        <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>90916</v>
+        <v>91029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6843,10 +6852,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>719309</v>
+        <v>719264</v>
       </c>
       <c r="R65" t="n">
-        <v>6373758</v>
+        <v>6374047</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6893,44 +6902,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128758579</v>
+        <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>86954</v>
+        <v>90916</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>4188</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6940,10 +6949,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>719375</v>
+        <v>719309</v>
       </c>
       <c r="R66" t="n">
-        <v>6374079</v>
+        <v>6373758</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,51 +6993,50 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128763912</v>
+        <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7038,10 +7046,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>719273</v>
+        <v>719375</v>
       </c>
       <c r="R67" t="n">
-        <v>6374077</v>
+        <v>6374079</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7082,50 +7090,51 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128763920</v>
+        <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>92819</v>
+        <v>86999</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1438</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7135,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>719342</v>
+        <v>719273</v>
       </c>
       <c r="R68" t="n">
-        <v>6373936</v>
+        <v>6374077</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7197,32 +7206,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128758616</v>
+        <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>86917</v>
+        <v>92819</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>1438</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon leucopus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7232,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>719364</v>
+        <v>719342</v>
       </c>
       <c r="R69" t="n">
-        <v>6374088</v>
+        <v>6373936</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7282,44 +7291,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128758577</v>
+        <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7329,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>719343</v>
+        <v>719364</v>
       </c>
       <c r="R70" t="n">
-        <v>6374082</v>
+        <v>6374088</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7373,7 +7382,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7392,32 +7400,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128763902</v>
+        <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7427,10 +7435,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>719304</v>
+        <v>719343</v>
       </c>
       <c r="R71" t="n">
-        <v>6373952</v>
+        <v>6374082</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7471,50 +7479,51 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128763923</v>
+        <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>92796</v>
+        <v>86999</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7524,10 +7533,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>719259</v>
+        <v>719304</v>
       </c>
       <c r="R72" t="n">
-        <v>6374086</v>
+        <v>6373952</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7586,32 +7595,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128763934</v>
+        <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>91029</v>
+        <v>92796</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7621,10 +7630,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>719273</v>
+        <v>719259</v>
       </c>
       <c r="R73" t="n">
-        <v>6374081</v>
+        <v>6374086</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7683,10 +7692,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128763905</v>
+        <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>86999</v>
+        <v>91029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7694,21 +7703,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7718,10 +7727,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>719245</v>
+        <v>719273</v>
       </c>
       <c r="R74" t="n">
-        <v>6374105</v>
+        <v>6374081</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7780,32 +7789,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128758578</v>
+        <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7815,10 +7824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>719382</v>
+        <v>719245</v>
       </c>
       <c r="R75" t="n">
-        <v>6374097</v>
+        <v>6374105</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7859,51 +7868,50 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128763938</v>
+        <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>56671</v>
+        <v>86954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208260</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7913,10 +7921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>719245</v>
+        <v>719382</v>
       </c>
       <c r="R76" t="n">
-        <v>6373863</v>
+        <v>6374097</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7957,21 +7965,119 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128763938</v>
+      </c>
+      <c r="B77" t="n">
+        <v>56671</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>719245</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6373863</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98641</v>
+        <v>98647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90916</v>
+        <v>90921</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98641</v>
+        <v>98647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86941</v>
+        <v>86945</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87148</v>
+        <v>87152</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86942</v>
+        <v>86946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87148</v>
+        <v>87152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90916</v>
+        <v>90921</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87030</v>
+        <v>87031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87030</v>
+        <v>87031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86934</v>
+        <v>86935</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90921</v>
+        <v>90926</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86945</v>
+        <v>86946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87152</v>
+        <v>87153</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86946</v>
+        <v>86947</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87152</v>
+        <v>87153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92824</v>
+        <v>92831</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106950</v>
+        <v>106957</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90921</v>
+        <v>90926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92824</v>
+        <v>92831</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87031</v>
+        <v>87035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87031</v>
+        <v>87035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86935</v>
+        <v>86939</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90926</v>
+        <v>90930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128758565</v>
       </c>
       <c r="B51" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86946</v>
+        <v>86950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87153</v>
+        <v>87157</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86947</v>
+        <v>86951</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87153</v>
+        <v>87157</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90926</v>
+        <v>90930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>128763938</v>
       </c>
       <c r="B77" t="n">
-        <v>56671</v>
+        <v>56674</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87035</v>
+        <v>87040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87035</v>
+        <v>87040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90930</v>
+        <v>90935</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128758565</v>
       </c>
       <c r="B51" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86950</v>
+        <v>86955</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87157</v>
+        <v>87162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86951</v>
+        <v>86956</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87157</v>
+        <v>87162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90930</v>
+        <v>90935</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>128763938</v>
       </c>
       <c r="B77" t="n">
-        <v>56674</v>
+        <v>56677</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87047</v>
+        <v>87050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87047</v>
+        <v>87050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90942</v>
+        <v>90945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110779</v>
+        <v>110784</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86962</v>
+        <v>86965</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87169</v>
+        <v>87172</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86963</v>
+        <v>86966</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87169</v>
+        <v>87172</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92848</v>
+        <v>92853</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106977</v>
+        <v>106982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90942</v>
+        <v>90945</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92848</v>
+        <v>92853</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87050</v>
+        <v>87053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87050</v>
+        <v>87053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90945</v>
+        <v>90948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110784</v>
+        <v>110787</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87172</v>
+        <v>87175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86966</v>
+        <v>86969</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87172</v>
+        <v>87175</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92853</v>
+        <v>92856</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106982</v>
+        <v>106985</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90945</v>
+        <v>90948</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92853</v>
+        <v>92856</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98681</v>
+        <v>98691</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87053</v>
+        <v>87057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87053</v>
+        <v>87057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98681</v>
+        <v>98691</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110787</v>
+        <v>110797</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128758565</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86968</v>
+        <v>86972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87175</v>
+        <v>87179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86969</v>
+        <v>86973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87175</v>
+        <v>87179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92856</v>
+        <v>92863</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106985</v>
+        <v>106995</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92856</v>
+        <v>92863</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>128763938</v>
       </c>
       <c r="B77" t="n">
-        <v>56677</v>
+        <v>56679</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98691</v>
+        <v>98698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87057</v>
+        <v>87064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87057</v>
+        <v>87064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>90959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98691</v>
+        <v>98698</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110797</v>
+        <v>110804</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86972</v>
+        <v>86979</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87179</v>
+        <v>87186</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86973</v>
+        <v>86980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87179</v>
+        <v>87186</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92863</v>
+        <v>92870</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>106995</v>
+        <v>107002</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90952</v>
+        <v>90959</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92863</v>
+        <v>92870</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128758608</v>
       </c>
       <c r="B2" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128758584</v>
       </c>
       <c r="B3" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128763928</v>
       </c>
       <c r="B4" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128758560</v>
       </c>
       <c r="B5" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128763925</v>
       </c>
       <c r="B6" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>128763914</v>
       </c>
       <c r="B7" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128758580</v>
       </c>
       <c r="B9" t="n">
-        <v>98698</v>
+        <v>98700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>128763927</v>
       </c>
       <c r="B10" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128758571</v>
       </c>
       <c r="B11" t="n">
-        <v>87064</v>
+        <v>87066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128758604</v>
       </c>
       <c r="B12" t="n">
-        <v>87064</v>
+        <v>87066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128758567</v>
       </c>
       <c r="B13" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128758570</v>
       </c>
       <c r="B14" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128758588</v>
       </c>
       <c r="B15" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128758593</v>
       </c>
       <c r="B16" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128758569</v>
       </c>
       <c r="B17" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128763943</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>128763951</v>
       </c>
       <c r="B19" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128758595</v>
       </c>
       <c r="B20" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>128758613</v>
       </c>
       <c r="B21" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>128763947</v>
       </c>
       <c r="B22" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128758612</v>
       </c>
       <c r="B23" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128763913</v>
       </c>
       <c r="B24" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128763935</v>
       </c>
       <c r="B25" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>128763940</v>
       </c>
       <c r="B26" t="n">
-        <v>90959</v>
+        <v>90961</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>128763915</v>
       </c>
       <c r="B27" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>128763932</v>
       </c>
       <c r="B28" t="n">
-        <v>98698</v>
+        <v>98700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128758615</v>
       </c>
       <c r="B29" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128758594</v>
       </c>
       <c r="B30" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128763924</v>
       </c>
       <c r="B31" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128758573</v>
       </c>
       <c r="B32" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128763956</v>
       </c>
       <c r="B33" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>128763911</v>
       </c>
       <c r="B34" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128763909</v>
       </c>
       <c r="B35" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128758568</v>
       </c>
       <c r="B36" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128758606</v>
       </c>
       <c r="B37" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>128758585</v>
       </c>
       <c r="B38" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128758574</v>
       </c>
       <c r="B40" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>128763944</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128763921</v>
       </c>
       <c r="B42" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128763952</v>
       </c>
       <c r="B43" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>128758563</v>
       </c>
       <c r="B44" t="n">
-        <v>110804</v>
+        <v>110806</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>128758576</v>
       </c>
       <c r="B46" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>128758614</v>
       </c>
       <c r="B47" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>128758592</v>
       </c>
       <c r="B48" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128758564</v>
       </c>
       <c r="B49" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128758611</v>
       </c>
       <c r="B50" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128758565</v>
       </c>
       <c r="B51" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>128763930</v>
       </c>
       <c r="B52" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>128763939</v>
       </c>
       <c r="B53" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128758609</v>
       </c>
       <c r="B54" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128758581</v>
       </c>
       <c r="B55" t="n">
-        <v>86979</v>
+        <v>86981</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87186</v>
+        <v>87188</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128763950</v>
       </c>
       <c r="B57" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86980</v>
+        <v>86982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87186</v>
+        <v>87188</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128758566</v>
       </c>
       <c r="B60" t="n">
-        <v>92870</v>
+        <v>92872</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128758589</v>
       </c>
       <c r="B62" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128758610</v>
       </c>
       <c r="B63" t="n">
-        <v>107002</v>
+        <v>107004</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128758587</v>
       </c>
       <c r="B64" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128758591</v>
       </c>
       <c r="B65" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128763941</v>
       </c>
       <c r="B66" t="n">
-        <v>90959</v>
+        <v>90961</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128758579</v>
       </c>
       <c r="B67" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128763912</v>
       </c>
       <c r="B68" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>128763920</v>
       </c>
       <c r="B69" t="n">
-        <v>92870</v>
+        <v>92872</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>128758616</v>
       </c>
       <c r="B70" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>128758577</v>
       </c>
       <c r="B71" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>128763902</v>
       </c>
       <c r="B72" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128763923</v>
       </c>
       <c r="B73" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>128763934</v>
       </c>
       <c r="B74" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>128763905</v>
       </c>
       <c r="B75" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128758578</v>
       </c>
       <c r="B76" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>128763938</v>
       </c>
       <c r="B77" t="n">
-        <v>56679</v>
+        <v>56681</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>128758603</v>
       </c>
       <c r="B8" t="n">
-        <v>86910</v>
+        <v>86911</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>128758605</v>
       </c>
       <c r="B45" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
         <v>128811138</v>
       </c>
       <c r="B58" t="n">
-        <v>86982</v>
+        <v>86983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87188</v>
+        <v>87189</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -6229,7 +6229,7 @@
         <v>128864739</v>
       </c>
       <c r="B59" t="n">
-        <v>87189</v>
+        <v>87192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87188</v>
+        <v>87166</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5941,24 +5941,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>451</v>
+        <v>3563</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
@@ -6001,6 +6004,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Sekvenserad</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87166</v>
+        <v>87167</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87167</v>
+        <v>87172</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87172</v>
+        <v>87176</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87176</v>
+        <v>87178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87178</v>
+        <v>87181</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87181</v>
+        <v>87184</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87184</v>
+        <v>87185</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -5933,7 +5933,7 @@
         <v>128758597</v>
       </c>
       <c r="B56" t="n">
-        <v>87185</v>
+        <v>87202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128758608</v>
+        <v>128758564</v>
       </c>
       <c r="B2" t="n">
-        <v>96274</v>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719059</v>
+        <v>719095</v>
       </c>
       <c r="R2" t="n">
-        <v>6373906</v>
+        <v>6373895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128758584</v>
+        <v>128763914</v>
       </c>
       <c r="B3" t="n">
-        <v>91074</v>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5747</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>719136</v>
+        <v>719218</v>
       </c>
       <c r="R3" t="n">
-        <v>6374115</v>
+        <v>6374100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128763928</v>
+        <v>128763915</v>
       </c>
       <c r="B4" t="n">
-        <v>86994</v>
+        <v>87193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719213</v>
+        <v>719198</v>
       </c>
       <c r="R4" t="n">
-        <v>6373874</v>
+        <v>6373941</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128758560</v>
+        <v>128763916</v>
       </c>
       <c r="B5" t="n">
-        <v>87039</v>
+        <v>87193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719126</v>
+        <v>719199</v>
       </c>
       <c r="R5" t="n">
-        <v>6374163</v>
+        <v>6373935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128763925</v>
+        <v>128763917</v>
       </c>
       <c r="B6" t="n">
-        <v>86994</v>
+        <v>87193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719139</v>
+        <v>719201</v>
       </c>
       <c r="R6" t="n">
-        <v>6374165</v>
+        <v>6373931</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1142,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1162,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128763914</v>
+        <v>128763918</v>
       </c>
       <c r="B7" t="n">
-        <v>86841</v>
+        <v>87193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719218</v>
+        <v>719201</v>
       </c>
       <c r="R7" t="n">
-        <v>6374100</v>
+        <v>6373928</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128758603</v>
+        <v>128758605</v>
       </c>
       <c r="B8" t="n">
-        <v>86911</v>
+        <v>87368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1270,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1294,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719231</v>
+        <v>719180</v>
       </c>
       <c r="R8" t="n">
-        <v>6374095</v>
+        <v>6373857</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,48 +1354,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128758580</v>
+        <v>128864739</v>
       </c>
       <c r="B9" t="n">
-        <v>98700</v>
+        <v>87540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>451</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>719133</v>
+        <v>719183</v>
       </c>
       <c r="R9" t="n">
-        <v>6374200</v>
+        <v>6373851</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1429,69 +1430,78 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bilder på Liams fynd. Finns ytterligare en inomhus på foten till höger PXL_20250928_195955265.RAW-01.COVER.jpg</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128763927</v>
+        <v>128811138</v>
       </c>
       <c r="B10" t="n">
-        <v>86994</v>
+        <v>87334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettrandad spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoglaucopus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>719184</v>
+        <v>719132</v>
       </c>
       <c r="R10" t="n">
-        <v>6373910</v>
+        <v>6374195</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,42 +1549,46 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128758571</v>
+        <v>128758566</v>
       </c>
       <c r="B11" t="n">
-        <v>87066</v>
+        <v>93234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>249249</v>
+        <v>1438</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grynspindling</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius olidoamethysteus s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Sarcodon leucopus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1582,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>719140</v>
+        <v>719264</v>
       </c>
       <c r="R11" t="n">
-        <v>6373973</v>
+        <v>6373868</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1626,7 +1640,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1645,30 +1658,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128758604</v>
+        <v>128763920</v>
       </c>
       <c r="B12" t="n">
-        <v>87066</v>
+        <v>93234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>249249</v>
+        <v>1438</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grynspindling</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius olidoamethysteus s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Sarcodon leucopus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>719109</v>
+        <v>719342</v>
       </c>
       <c r="R12" t="n">
-        <v>6373955</v>
+        <v>6373936</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,44 +1743,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128758567</v>
+        <v>128758595</v>
       </c>
       <c r="B13" t="n">
-        <v>86795</v>
+        <v>87322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>719130</v>
+        <v>719185</v>
       </c>
       <c r="R13" t="n">
-        <v>6374180</v>
+        <v>6373860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128758570</v>
+        <v>128758596</v>
       </c>
       <c r="B14" t="n">
-        <v>86795</v>
+        <v>87322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>719161</v>
+        <v>719323</v>
       </c>
       <c r="R14" t="n">
-        <v>6373872</v>
+        <v>6373849</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1932,32 +1949,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128758588</v>
+        <v>128758608</v>
       </c>
       <c r="B15" t="n">
-        <v>91074</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5747</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>719228</v>
+        <v>719059</v>
       </c>
       <c r="R15" t="n">
-        <v>6374050</v>
+        <v>6373906</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128758593</v>
+        <v>128758597</v>
       </c>
       <c r="B16" t="n">
-        <v>91074</v>
+        <v>87473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,34 +2057,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5747</v>
+        <v>3563</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>719228</v>
+        <v>719183</v>
       </c>
       <c r="R16" t="n">
-        <v>6374089</v>
+        <v>6373852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2102,12 +2122,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sekvenserad</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2126,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128758569</v>
+        <v>128758581</v>
       </c>
       <c r="B17" t="n">
-        <v>86795</v>
+        <v>87333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3762</v>
+        <v>3599</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>719168</v>
+        <v>719062</v>
       </c>
       <c r="R17" t="n">
-        <v>6374009</v>
+        <v>6373899</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2249,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128763943</v>
+        <v>128758611</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>87309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2260,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>719213</v>
+        <v>719194</v>
       </c>
       <c r="R18" t="n">
-        <v>6374141</v>
+        <v>6373878</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2302,29 +2328,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128763951</v>
+        <v>128758612</v>
       </c>
       <c r="B19" t="n">
-        <v>86819</v>
+        <v>87309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2332,21 +2357,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2356,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>719186</v>
+        <v>719165</v>
       </c>
       <c r="R19" t="n">
-        <v>6373931</v>
+        <v>6373921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,22 +2431,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128758595</v>
+        <v>128758613</v>
       </c>
       <c r="B20" t="n">
-        <v>86970</v>
+        <v>87309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2429,21 +2454,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2453,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>719185</v>
+        <v>719153</v>
       </c>
       <c r="R20" t="n">
-        <v>6373860</v>
+        <v>6373906</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2515,10 +2540,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128758613</v>
+        <v>128758614</v>
       </c>
       <c r="B21" t="n">
-        <v>86957</v>
+        <v>87309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>719153</v>
+        <v>719186</v>
       </c>
       <c r="R21" t="n">
-        <v>6373906</v>
+        <v>6373853</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2612,10 +2637,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128763947</v>
+        <v>128758615</v>
       </c>
       <c r="B22" t="n">
-        <v>86819</v>
+        <v>87309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2623,21 +2648,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2647,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>719124</v>
+        <v>719126</v>
       </c>
       <c r="R22" t="n">
-        <v>6374154</v>
+        <v>6374002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,22 +2722,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128758612</v>
+        <v>128758616</v>
       </c>
       <c r="B23" t="n">
-        <v>86957</v>
+        <v>87309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>719165</v>
+        <v>719364</v>
       </c>
       <c r="R23" t="n">
-        <v>6373921</v>
+        <v>6374088</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2806,10 +2831,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128763913</v>
+        <v>128763952</v>
       </c>
       <c r="B24" t="n">
-        <v>91048</v>
+        <v>87309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2817,21 +2842,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2841,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>719198</v>
+        <v>719195</v>
       </c>
       <c r="R24" t="n">
-        <v>6374009</v>
+        <v>6373936</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2903,32 +2928,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128763935</v>
+        <v>128763953</v>
       </c>
       <c r="B25" t="n">
-        <v>91074</v>
+        <v>87309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2938,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>719192</v>
+        <v>719198</v>
       </c>
       <c r="R25" t="n">
-        <v>6373934</v>
+        <v>6373928</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3000,10 +3025,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128763940</v>
+        <v>128763955</v>
       </c>
       <c r="B26" t="n">
-        <v>90961</v>
+        <v>87309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,21 +3036,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3035,10 +3060,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>719220</v>
+        <v>719188</v>
       </c>
       <c r="R26" t="n">
-        <v>6374101</v>
+        <v>6373931</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3097,32 +3122,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128763915</v>
+        <v>128763956</v>
       </c>
       <c r="B27" t="n">
-        <v>86841</v>
+        <v>87309</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3132,10 +3157,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>719198</v>
+        <v>719166</v>
       </c>
       <c r="R27" t="n">
-        <v>6373941</v>
+        <v>6373921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3194,32 +3219,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128763932</v>
+        <v>128758609</v>
       </c>
       <c r="B28" t="n">
-        <v>98700</v>
+        <v>87170</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219862</v>
+        <v>3712</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3229,10 +3254,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>719160</v>
+        <v>719158</v>
       </c>
       <c r="R28" t="n">
-        <v>6374175</v>
+        <v>6373915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3279,44 +3304,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128758615</v>
+        <v>128763947</v>
       </c>
       <c r="B29" t="n">
-        <v>86957</v>
+        <v>87170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3326,10 +3351,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>719126</v>
+        <v>719124</v>
       </c>
       <c r="R29" t="n">
-        <v>6374002</v>
+        <v>6374154</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3376,44 +3401,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128758594</v>
+        <v>128763950</v>
       </c>
       <c r="B30" t="n">
-        <v>91074</v>
+        <v>87170</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>3712</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3423,10 +3448,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>719216</v>
+        <v>719190</v>
       </c>
       <c r="R30" t="n">
-        <v>6374124</v>
+        <v>6373934</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3473,44 +3498,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128763924</v>
+        <v>128763951</v>
       </c>
       <c r="B31" t="n">
-        <v>86795</v>
+        <v>87170</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3520,10 +3545,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>719135</v>
+        <v>719186</v>
       </c>
       <c r="R31" t="n">
-        <v>6374160</v>
+        <v>6373931</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3582,32 +3607,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128758573</v>
+        <v>128758567</v>
       </c>
       <c r="B32" t="n">
-        <v>86994</v>
+        <v>87146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3617,10 +3642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>719123</v>
+        <v>719130</v>
       </c>
       <c r="R32" t="n">
-        <v>6373932</v>
+        <v>6374180</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3661,7 +3686,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3680,10 +3704,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128763956</v>
+        <v>128758568</v>
       </c>
       <c r="B33" t="n">
-        <v>86957</v>
+        <v>87146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3691,21 +3715,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3715,10 +3739,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>719166</v>
+        <v>719125</v>
       </c>
       <c r="R33" t="n">
-        <v>6373921</v>
+        <v>6373935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3765,44 +3789,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128763911</v>
+        <v>128758569</v>
       </c>
       <c r="B34" t="n">
-        <v>87039</v>
+        <v>87146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3812,10 +3836,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>719191</v>
+        <v>719168</v>
       </c>
       <c r="R34" t="n">
-        <v>6373892</v>
+        <v>6374009</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3862,44 +3886,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128763909</v>
+        <v>128758570</v>
       </c>
       <c r="B35" t="n">
-        <v>87039</v>
+        <v>87146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3909,10 +3933,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>719170</v>
+        <v>719161</v>
       </c>
       <c r="R35" t="n">
-        <v>6373908</v>
+        <v>6373872</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3959,22 +3983,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128758568</v>
+        <v>128763924</v>
       </c>
       <c r="B36" t="n">
-        <v>86795</v>
+        <v>87146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4006,10 +4030,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>719125</v>
+        <v>719135</v>
       </c>
       <c r="R36" t="n">
-        <v>6373935</v>
+        <v>6374160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4056,22 +4080,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128758606</v>
+        <v>128758560</v>
       </c>
       <c r="B37" t="n">
-        <v>86910</v>
+        <v>87391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4079,21 +4103,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4103,10 +4127,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>719123</v>
+        <v>719126</v>
       </c>
       <c r="R37" t="n">
-        <v>6374156</v>
+        <v>6374163</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4165,10 +4189,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128758585</v>
+        <v>128763902</v>
       </c>
       <c r="B38" t="n">
-        <v>91074</v>
+        <v>87391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4176,21 +4200,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4200,10 +4224,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>719136</v>
+        <v>719304</v>
       </c>
       <c r="R38" t="n">
-        <v>6374072</v>
+        <v>6373952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4250,44 +4274,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128758582</v>
+        <v>128763905</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>87391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>3767</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4297,10 +4321,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>719122</v>
+        <v>719245</v>
       </c>
       <c r="R39" t="n">
-        <v>6373999</v>
+        <v>6374105</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4347,44 +4371,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128758574</v>
+        <v>128763907</v>
       </c>
       <c r="B40" t="n">
-        <v>86994</v>
+        <v>87391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4394,10 +4418,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>719119</v>
+        <v>719188</v>
       </c>
       <c r="R40" t="n">
-        <v>6373869</v>
+        <v>6373928</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4438,67 +4462,63 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128763944</v>
+        <v>128763908</v>
       </c>
       <c r="B41" t="n">
-        <v>92871</v>
+        <v>87391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>3767</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>719136</v>
+        <v>719183</v>
       </c>
       <c r="R41" t="n">
-        <v>6374164</v>
+        <v>6373925</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4539,7 +4559,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4558,32 +4577,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128763921</v>
+        <v>128763909</v>
       </c>
       <c r="B42" t="n">
-        <v>92847</v>
+        <v>87391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4593,10 +4612,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>719130</v>
+        <v>719170</v>
       </c>
       <c r="R42" t="n">
-        <v>6374157</v>
+        <v>6373908</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4655,32 +4674,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128763952</v>
+        <v>128763911</v>
       </c>
       <c r="B43" t="n">
-        <v>86957</v>
+        <v>87391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4690,10 +4709,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>719195</v>
+        <v>719191</v>
       </c>
       <c r="R43" t="n">
-        <v>6373936</v>
+        <v>6373892</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4752,32 +4771,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128758563</v>
+        <v>128763912</v>
       </c>
       <c r="B44" t="n">
-        <v>110806</v>
+        <v>87391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219711</v>
+        <v>3767</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4787,10 +4806,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>719153</v>
+        <v>719273</v>
       </c>
       <c r="R44" t="n">
-        <v>6373918</v>
+        <v>6374077</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4837,44 +4856,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128758605</v>
+        <v>128763940</v>
       </c>
       <c r="B45" t="n">
-        <v>87017</v>
+        <v>91322</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>449</v>
+        <v>4188</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4884,10 +4903,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>719180</v>
+        <v>719220</v>
       </c>
       <c r="R45" t="n">
-        <v>6373857</v>
+        <v>6374101</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4934,44 +4953,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128758576</v>
+        <v>128763941</v>
       </c>
       <c r="B46" t="n">
-        <v>86994</v>
+        <v>91322</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>4188</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4981,10 +5000,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>719163</v>
+        <v>719309</v>
       </c>
       <c r="R46" t="n">
-        <v>6373923</v>
+        <v>6373758</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5025,51 +5044,50 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128758614</v>
+        <v>128763921</v>
       </c>
       <c r="B47" t="n">
-        <v>86957</v>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5079,10 +5097,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>719186</v>
+        <v>719130</v>
       </c>
       <c r="R47" t="n">
-        <v>6373853</v>
+        <v>6374157</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5129,44 +5147,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128758592</v>
+        <v>128763922</v>
       </c>
       <c r="B48" t="n">
-        <v>91074</v>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5176,10 +5194,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>719236</v>
+        <v>719198</v>
       </c>
       <c r="R48" t="n">
-        <v>6374081</v>
+        <v>6373928</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5226,44 +5244,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128758564</v>
+        <v>128763923</v>
       </c>
       <c r="B49" t="n">
-        <v>86841</v>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5273,10 +5291,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>719095</v>
+        <v>719259</v>
       </c>
       <c r="R49" t="n">
-        <v>6373895</v>
+        <v>6374086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5323,44 +5341,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128758611</v>
+        <v>128763913</v>
       </c>
       <c r="B50" t="n">
-        <v>86957</v>
+        <v>91409</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5370,10 +5388,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>719194</v>
+        <v>719198</v>
       </c>
       <c r="R50" t="n">
-        <v>6373878</v>
+        <v>6374009</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5420,65 +5438,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128758565</v>
+        <v>128758584</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>91435</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>719213</v>
+        <v>719136</v>
       </c>
       <c r="R51" t="n">
-        <v>6373874</v>
+        <v>6374115</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5537,32 +5547,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128763930</v>
+        <v>128758585</v>
       </c>
       <c r="B52" t="n">
-        <v>86994</v>
+        <v>91435</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5572,10 +5582,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>719235</v>
+        <v>719136</v>
       </c>
       <c r="R52" t="n">
-        <v>6374103</v>
+        <v>6374072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5616,29 +5626,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128763939</v>
+        <v>128758587</v>
       </c>
       <c r="B53" t="n">
-        <v>86910</v>
+        <v>91435</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5646,37 +5655,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>248956</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>719236</v>
+        <v>719350</v>
       </c>
       <c r="R53" t="n">
-        <v>6374106</v>
+        <v>6373915</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5717,51 +5723,50 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128758609</v>
+        <v>128758588</v>
       </c>
       <c r="B54" t="n">
-        <v>86819</v>
+        <v>91435</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5771,10 +5776,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>719158</v>
+        <v>719228</v>
       </c>
       <c r="R54" t="n">
-        <v>6373915</v>
+        <v>6374050</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5833,10 +5838,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128758581</v>
+        <v>128758589</v>
       </c>
       <c r="B55" t="n">
-        <v>86981</v>
+        <v>91435</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5844,21 +5849,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5868,10 +5873,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>719062</v>
+        <v>719240</v>
       </c>
       <c r="R55" t="n">
-        <v>6373899</v>
+        <v>6374049</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5930,10 +5935,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128758597</v>
+        <v>128758591</v>
       </c>
       <c r="B56" t="n">
-        <v>87217</v>
+        <v>91435</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5941,37 +5946,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3563</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>719183</v>
+        <v>719264</v>
       </c>
       <c r="R56" t="n">
-        <v>6373852</v>
+        <v>6374047</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6006,18 +6008,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Sekvenserad</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6036,32 +6032,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128763950</v>
+        <v>128758592</v>
       </c>
       <c r="B57" t="n">
-        <v>86819</v>
+        <v>91435</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6071,10 +6067,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>719190</v>
+        <v>719236</v>
       </c>
       <c r="R57" t="n">
-        <v>6373934</v>
+        <v>6374081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6121,22 +6117,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128811138</v>
+        <v>128758593</v>
       </c>
       <c r="B58" t="n">
-        <v>86983</v>
+        <v>91435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,37 +6140,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>462</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettrandad spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoglaucopus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>719132</v>
+        <v>719228</v>
       </c>
       <c r="R58" t="n">
-        <v>6374195</v>
+        <v>6374089</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6215,7 +6208,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6227,17 +6219,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128864739</v>
+        <v>128758594</v>
       </c>
       <c r="B59" t="n">
-        <v>87192</v>
+        <v>91435</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,40 +6237,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>451</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>719183</v>
+        <v>719216</v>
       </c>
       <c r="R59" t="n">
-        <v>6373851</v>
+        <v>6374124</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,62 +6299,56 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Bilder på Liams fynd. Finns ytterligare en inomhus på foten till höger PXL_20250928_195955265.RAW-01.COVER.jpg</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128758566</v>
+        <v>128763934</v>
       </c>
       <c r="B60" t="n">
-        <v>92872</v>
+        <v>91435</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1438</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6375,10 +6358,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>719264</v>
+        <v>719273</v>
       </c>
       <c r="R60" t="n">
-        <v>6373868</v>
+        <v>6374081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6425,44 +6408,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128758583</v>
+        <v>128763935</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>91435</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6455,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>719299</v>
+        <v>719192</v>
       </c>
       <c r="R61" t="n">
-        <v>6373884</v>
+        <v>6373934</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6522,44 +6505,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128758589</v>
+        <v>128763943</v>
       </c>
       <c r="B62" t="n">
-        <v>91074</v>
+        <v>93233</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>719240</v>
+        <v>719213</v>
       </c>
       <c r="R62" t="n">
-        <v>6374049</v>
+        <v>6374141</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6613,28 +6596,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128758610</v>
+        <v>128763944</v>
       </c>
       <c r="B63" t="n">
-        <v>107004</v>
+        <v>93233</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6642,34 +6626,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221849</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>719323</v>
+        <v>719136</v>
       </c>
       <c r="R63" t="n">
-        <v>6374030</v>
+        <v>6374164</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6710,63 +6697,67 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128758587</v>
+        <v>128763945</v>
       </c>
       <c r="B64" t="n">
-        <v>91074</v>
+        <v>93233</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>719350</v>
+        <v>719201</v>
       </c>
       <c r="R64" t="n">
-        <v>6373915</v>
+        <v>6373931</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,63 +6798,67 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128758591</v>
+        <v>128763946</v>
       </c>
       <c r="B65" t="n">
-        <v>91074</v>
+        <v>93233</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>719264</v>
+        <v>719183</v>
       </c>
       <c r="R65" t="n">
-        <v>6374047</v>
+        <v>6373923</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6904,50 +6899,51 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128763941</v>
+        <v>128758599</v>
       </c>
       <c r="B66" t="n">
-        <v>90961</v>
+        <v>75428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4188</v>
+        <v>6426</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6957,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>719309</v>
+        <v>719199</v>
       </c>
       <c r="R66" t="n">
-        <v>6373758</v>
+        <v>6373839</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7007,57 +7003,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128758579</v>
+        <v>128758565</v>
       </c>
       <c r="B67" t="n">
-        <v>86994</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>719375</v>
+        <v>719213</v>
       </c>
       <c r="R67" t="n">
-        <v>6374079</v>
+        <v>6373874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7098,7 +7102,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7117,32 +7120,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128763912</v>
+        <v>128758582</v>
       </c>
       <c r="B68" t="n">
-        <v>87039</v>
+        <v>8455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7152,10 +7155,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>719273</v>
+        <v>719122</v>
       </c>
       <c r="R68" t="n">
-        <v>6374077</v>
+        <v>6373999</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7202,44 +7205,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128763920</v>
+        <v>128758583</v>
       </c>
       <c r="B69" t="n">
-        <v>92872</v>
+        <v>8455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1438</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7249,10 +7252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>719342</v>
+        <v>719299</v>
       </c>
       <c r="R69" t="n">
-        <v>6373936</v>
+        <v>6373884</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7299,60 +7302,81 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128758616</v>
+        <v>95513805</v>
       </c>
       <c r="B70" t="n">
-        <v>86957</v>
+        <v>43219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>201028</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Kräklingbo Gurpe 1:66, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>719364</v>
+        <v>719319</v>
       </c>
       <c r="R70" t="n">
-        <v>6374088</v>
+        <v>6373730</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7376,12 +7400,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7390,50 +7414,51 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128758577</v>
+        <v>128763938</v>
       </c>
       <c r="B71" t="n">
-        <v>86994</v>
+        <v>56905</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>208260</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>719343</v>
+        <v>719245</v>
       </c>
       <c r="R71" t="n">
-        <v>6374082</v>
+        <v>6373863</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7487,51 +7512,50 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128763902</v>
+        <v>128758563</v>
       </c>
       <c r="B72" t="n">
-        <v>87039</v>
+        <v>111389</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3767</v>
+        <v>219711</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7541,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>719304</v>
+        <v>719153</v>
       </c>
       <c r="R72" t="n">
-        <v>6373952</v>
+        <v>6373918</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7591,22 +7615,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128763923</v>
+        <v>128758580</v>
       </c>
       <c r="B73" t="n">
-        <v>92847</v>
+        <v>99141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>219862</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>719259</v>
+        <v>719133</v>
       </c>
       <c r="R73" t="n">
-        <v>6374086</v>
+        <v>6374200</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7688,44 +7712,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128763934</v>
+        <v>128763932</v>
       </c>
       <c r="B74" t="n">
-        <v>91074</v>
+        <v>99141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5747</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7735,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>719273</v>
+        <v>719160</v>
       </c>
       <c r="R74" t="n">
-        <v>6374081</v>
+        <v>6374175</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,32 +7821,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128763905</v>
+        <v>128758610</v>
       </c>
       <c r="B75" t="n">
-        <v>87039</v>
+        <v>107516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7832,10 +7856,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>719245</v>
+        <v>719323</v>
       </c>
       <c r="R75" t="n">
-        <v>6374105</v>
+        <v>6374030</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7882,44 +7906,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128758578</v>
+        <v>128758603</v>
       </c>
       <c r="B76" t="n">
-        <v>86994</v>
+        <v>87262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7929,10 +7953,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>719382</v>
+        <v>719231</v>
       </c>
       <c r="R76" t="n">
-        <v>6374097</v>
+        <v>6374095</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7973,7 +7997,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -7992,32 +8015,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128763938</v>
+        <v>128758606</v>
       </c>
       <c r="B77" t="n">
-        <v>56681</v>
+        <v>87262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>208260</v>
+        <v>248956</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8027,10 +8050,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>719245</v>
+        <v>719123</v>
       </c>
       <c r="R77" t="n">
-        <v>6373863</v>
+        <v>6374156</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8077,15 +8100,1577 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128763939</v>
+      </c>
+      <c r="B78" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>719236</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6374106</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128758571</v>
+      </c>
+      <c r="B79" t="n">
+        <v>87418</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>249249</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Grynspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius olidoamethysteus s.lat.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>719140</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6373973</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128758604</v>
+      </c>
+      <c r="B80" t="n">
+        <v>87418</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>249249</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Grynspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius olidoamethysteus s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>719109</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6373955</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128758573</v>
+      </c>
+      <c r="B81" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>719123</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6373932</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128758574</v>
+      </c>
+      <c r="B82" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>719119</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6373869</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128758575</v>
+      </c>
+      <c r="B83" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>719137</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6373850</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128758576</v>
+      </c>
+      <c r="B84" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>719163</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6373923</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128758577</v>
+      </c>
+      <c r="B85" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>719343</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6374082</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128758578</v>
+      </c>
+      <c r="B86" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>719382</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6374097</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128758579</v>
+      </c>
+      <c r="B87" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>719375</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6374079</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128763925</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>719139</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6374165</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128763926</v>
+      </c>
+      <c r="B89" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>719189</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6373928</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128763927</v>
+      </c>
+      <c r="B90" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>719184</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6373910</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128763928</v>
+      </c>
+      <c r="B91" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>719213</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6373874</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128763930</v>
+      </c>
+      <c r="B92" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>719235</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6374103</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128763931</v>
+      </c>
+      <c r="B93" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>719184</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6373924</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45536-2025 artfynd.xlsx
+++ b/artfynd/A 45536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763914</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763915</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763916</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758605</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864739</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811138</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758566</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763920</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758595</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758596</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758608</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2149,6 +2224,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758597</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758581</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758611</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2440,6 +2530,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758612</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2537,6 +2632,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758613</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2634,6 +2734,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758614</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2731,6 +2836,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758615</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758616</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2925,6 +3040,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763952</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3022,6 +3142,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763953</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3119,6 +3244,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763955</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3216,6 +3346,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763956</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3313,6 +3448,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758609</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3410,6 +3550,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763947</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3507,6 +3652,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763950</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3604,6 +3754,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763951</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3701,6 +3856,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758567</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3798,6 +3958,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758568</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3895,6 +4060,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758569</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3992,6 +4162,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758570</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4089,6 +4264,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763924</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4186,6 +4366,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758560</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4283,6 +4468,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763902</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4380,6 +4570,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763905</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4477,6 +4672,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763907</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4574,6 +4774,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763908</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4671,6 +4876,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763909</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4768,6 +4978,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763911</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4865,6 +5080,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763912</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4962,6 +5182,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763940</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5059,6 +5284,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763941</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5156,6 +5386,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763921</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5253,6 +5488,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763922</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5350,6 +5590,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763923</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5447,6 +5692,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763913</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5544,6 +5794,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758584</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5641,6 +5896,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758585</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5738,6 +5998,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758587</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5835,6 +6100,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758588</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5932,6 +6202,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758589</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6029,6 +6304,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758591</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6126,6 +6406,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758592</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6223,6 +6508,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758593</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6320,6 +6610,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758594</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6417,6 +6712,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763934</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6514,6 +6814,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763935</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6612,6 +6917,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763943</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6713,6 +7023,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763944</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6814,6 +7129,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763945</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6915,6 +7235,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763946</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7012,6 +7337,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758599</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7117,6 +7447,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758565</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7214,6 +7549,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758582</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7311,6 +7651,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758583</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7430,6 +7775,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95513805</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7527,6 +7877,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763938</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7624,6 +7979,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758563</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7721,6 +8081,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758580</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7818,6 +8183,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763932</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7915,6 +8285,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758610</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8012,6 +8387,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758603</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8109,6 +8489,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758606</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8210,6 +8595,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763939</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8304,6 +8694,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758571</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8397,6 +8792,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758604</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8495,6 +8895,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758573</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8593,6 +8998,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758574</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8691,6 +9101,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758575</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8789,6 +9204,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758576</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8887,6 +9307,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758577</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8985,6 +9410,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758578</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9083,6 +9513,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758579</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9181,6 +9616,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763925</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9279,6 +9719,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763926</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9377,6 +9822,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763927</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9475,6 +9925,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763928</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9573,6 +10028,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763930</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9671,8 +10131,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>